--- a/education_surveys/023_favorite_quotes_survey--education_surveys.xlsx
+++ b/education_surveys/023_favorite_quotes_survey--education_surveys.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -722,7 +722,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Favorite Quote Category</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,7 +745,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Favorite Quote Source</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -791,7 +791,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Book Other</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -814,7 +814,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Favorite Book Category</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>Favorite Book Source</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Quote Category Other</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -929,7 +929,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Quote Source Other</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -952,7 +952,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Favorite Quote Source Category</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -975,7 +975,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Book Other Source</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -993,12 +993,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>favorite_book_other_source</t>
+          <t>favorite_book_other_source_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Book Other Source 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Favorite Book Other Category</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Favorite Book Other Source Other</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>favorite_book_category</t>
+          <t>favorite_book_category_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Favorite Book Category 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
